--- a/site/Set-Up-Webhooks-in-UKG-Ready/headings.xlsx
+++ b/site/Set-Up-Webhooks-in-UKG-Ready/headings.xlsx
@@ -463,7 +463,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Prerequisite</t>
+          <t>Prerequisites</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">

--- a/site/Set-Up-Webhooks-in-UKG-Ready/headings.xlsx
+++ b/site/Set-Up-Webhooks-in-UKG-Ready/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -501,6 +501,28 @@
       <c r="D4" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Ready/#h_01JRASF19YVF6K69BV8Q14240R</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Reference</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01M0CKP4QX07F98P5MREMX9TCW</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Ready/#h_01M0CKP4QX07F98P5MREMX9TCW</t>
         </is>
       </c>
     </row>

--- a/site/Set-Up-Webhooks-in-UKG-Ready/headings.xlsx
+++ b/site/Set-Up-Webhooks-in-UKG-Ready/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,20 +507,42 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Obtaining Event URL and Token</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>h_01KX5QP1B74WSDXK6Y7JQ3A416</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Ready/#h_01KX5QP1B74WSDXK6Y7JQ3A416</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Reference</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>h_01M0CKP4QX07F98P5MREMX9TCW</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Set-Up-Webhooks-in-UKG-Ready/#h_01M0CKP4QX07F98P5MREMX9TCW</t>
         </is>
